--- a/data/source/weekly/cs-en-us-108pct.xlsx
+++ b/data/source/weekly/cs-en-us-108pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -873,7 +873,7 @@
         <v>20</v>
       </c>
       <c r="J14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" s="15">
         <v>-100</v>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>0</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>4</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J15" s="14">
         <v>2</v>
       </c>
       <c r="K15" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M15" s="15">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="N15" s="15">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
         <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>25</v>
+        <v>-25</v>
       </c>
       <c r="F16" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G16" s="14">
         <v>12</v>
       </c>
       <c r="H16" s="15">
-        <v>-16.666666666666</v>
+        <v>8.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J16" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K16" s="15">
-        <v>20</v>
+        <v>10.526315789473</v>
       </c>
       <c r="L16" s="15">
-        <v>-30.769230769230</v>
+        <v>-32.258064516129</v>
       </c>
       <c r="M16" s="15">
-        <v>-41.935483870967</v>
+        <v>-38.235294117647</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.461538461538</v>
+        <v>-88</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>-16.666666666666</v>
+        <v>300</v>
       </c>
       <c r="F17" s="14">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G17" s="14">
         <v>18</v>
       </c>
       <c r="H17" s="15">
-        <v>5.555555555555</v>
+        <v>50</v>
       </c>
       <c r="I17" s="14">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="J17" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K17" s="15">
-        <v>4.166666666666</v>
+        <v>30.769230769230</v>
       </c>
       <c r="L17" s="15">
-        <v>19.047619047619</v>
+        <v>21.428571428571</v>
       </c>
       <c r="M17" s="15">
-        <v>92.307692307692</v>
+        <v>142.857142857143</v>
       </c>
       <c r="N17" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
         <v>2</v>
       </c>
-      <c r="D18" s="14">
-        <v>8</v>
-      </c>
       <c r="E18" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
         <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H18" s="15">
-        <v>-59.090909090909</v>
+        <v>-55</v>
       </c>
       <c r="I18" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J18" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K18" s="15">
-        <v>-40</v>
+        <v>-37.5</v>
       </c>
       <c r="L18" s="15">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M18" s="15">
-        <v>-28</v>
+        <v>-31.034482758620</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.535031847133</v>
+        <v>-89.189189189189</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E19" s="15">
-        <v>33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="F19" s="14">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="G19" s="14">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H19" s="15">
-        <v>31.111111111111</v>
+        <v>8.333333333333</v>
       </c>
       <c r="I19" s="14">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J19" s="14">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="K19" s="15">
-        <v>46.296296296296</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L19" s="15">
-        <v>-7.058823529411</v>
+        <v>-7.216494845360</v>
       </c>
       <c r="M19" s="15">
-        <v>83.720930232558</v>
+        <v>80</v>
       </c>
       <c r="N19" s="15">
-        <v>-7.058823529411</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="F20" s="14">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G20" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H20" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="I20" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J20" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K20" s="15">
-        <v>169.230769230769</v>
+        <v>111.764705882353</v>
       </c>
       <c r="L20" s="15">
-        <v>169.230769230769</v>
+        <v>100</v>
       </c>
       <c r="M20" s="15">
-        <v>40</v>
+        <v>28.571428571428</v>
       </c>
       <c r="N20" s="15">
-        <v>-84.848484848484</v>
+        <v>-86.617100371747</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D21" s="17">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E21" s="18">
-        <v>-5.555555555555</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="F21" s="17">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G21" s="17">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H21" s="18">
-        <v>15.740740740740</v>
+        <v>9.090909090909</v>
       </c>
       <c r="I21" s="17">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="J21" s="17">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="K21" s="18">
-        <v>29.496402877697</v>
+        <v>23.214285714285</v>
       </c>
       <c r="L21" s="18">
-        <v>6.508875739644</v>
+        <v>1.470588235294</v>
       </c>
       <c r="M21" s="18">
-        <v>29.496402877697</v>
+        <v>31.847133757961</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.768532526475</v>
+        <v>-72.941176470588</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>4</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D22" s="14">
+        <v>3</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-66.666666666666</v>
       </c>
       <c r="F22" s="14">
         <v>8</v>
       </c>
       <c r="G22" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>700</v>
+        <v>166.666666666667</v>
       </c>
       <c r="I22" s="14">
         <v>10</v>
       </c>
       <c r="J22" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K22" s="15">
-        <v>900</v>
+        <v>150</v>
       </c>
       <c r="L22" s="15">
-        <v>233.333333333333</v>
+        <v>150</v>
       </c>
       <c r="M22" s="15">
-        <v>100</v>
+        <v>42.857142857142</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="D24" s="14">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E24" s="15">
-        <v>-3.333333333333</v>
+        <v>138.888888888889</v>
       </c>
       <c r="F24" s="14">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="G24" s="14">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="H24" s="15">
-        <v>-1.694915254237</v>
+        <v>15.887850467289</v>
       </c>
       <c r="I24" s="14">
-        <v>153</v>
+        <v>196</v>
       </c>
       <c r="J24" s="14">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="K24" s="15">
-        <v>-14.525139664804</v>
+        <v>-0.507614213197</v>
       </c>
       <c r="L24" s="15">
-        <v>-30.769230769230</v>
+        <v>-25.757575757575</v>
       </c>
       <c r="M24" s="15">
-        <v>106.756756756757</v>
+        <v>139.024390243902</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="D25" s="14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15">
-        <v>41.666666666666</v>
+        <v>337.5</v>
       </c>
       <c r="F25" s="14">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="G25" s="14">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H25" s="15">
-        <v>-1.538461538461</v>
+        <v>40</v>
       </c>
       <c r="I25" s="14">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="J25" s="14">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="K25" s="15">
-        <v>-18.446601941747</v>
+        <v>7.207207207207</v>
       </c>
       <c r="L25" s="15">
-        <v>-36.842105263157</v>
+        <v>-25.157232704402</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F26" s="14">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G26" s="14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H26" s="15">
-        <v>34.615384615384</v>
+        <v>41.666666666666</v>
       </c>
       <c r="I26" s="14">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="J26" s="14">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="K26" s="15">
-        <v>11.904761904761</v>
+        <v>13.725490196078</v>
       </c>
       <c r="L26" s="15">
-        <v>-6</v>
+        <v>-4.918032786885</v>
       </c>
       <c r="M26" s="15">
-        <v>-14.545454545454</v>
+        <v>-15.942028985507</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>2</v>
-      </c>
-      <c r="D27" s="14">
-        <v>2</v>
-      </c>
-      <c r="E27" s="15">
-        <v>0</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>5</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>66.666666666666</v>
+        <v>150</v>
       </c>
       <c r="I27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J27" s="14">
         <v>4</v>
       </c>
       <c r="K27" s="15">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="L27" s="15">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,23 +1425,23 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>2</v>
-      </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
         <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I28" s="14">
         <v>5</v>
@@ -1453,7 +1453,7 @@
         <v>66.666666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>-28.571428571428</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1566,8 +1566,8 @@
       <c r="H31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
+      <c r="I31" s="14">
+        <v>1</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-108pct.xlsx
+++ b/data/source/weekly/cs-en-us-108pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -895,29 +895,29 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
         <v>6</v>
       </c>
       <c r="J15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>21</v>
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>-25</v>
+        <v>100</v>
       </c>
       <c r="F16" s="14">
         <v>13</v>
@@ -952,22 +952,22 @@
         <v>8.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J16" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K16" s="15">
-        <v>10.526315789473</v>
+        <v>15</v>
       </c>
       <c r="L16" s="15">
-        <v>-32.258064516129</v>
+        <v>-28.125</v>
       </c>
       <c r="M16" s="15">
-        <v>-38.235294117647</v>
+        <v>-32.352941176470</v>
       </c>
       <c r="N16" s="15">
-        <v>-88</v>
+        <v>-87.700534759358</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>300</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G17" s="14">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H17" s="15">
-        <v>50</v>
+        <v>85.714285714285</v>
       </c>
       <c r="I17" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J17" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K17" s="15">
-        <v>30.769230769230</v>
+        <v>31.034482758620</v>
       </c>
       <c r="L17" s="15">
-        <v>21.428571428571</v>
+        <v>11.764705882352</v>
       </c>
       <c r="M17" s="15">
-        <v>142.857142857143</v>
+        <v>153.333333333333</v>
       </c>
       <c r="N17" s="15">
-        <v>0</v>
+        <v>2.702702702702</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
         <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
         <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H18" s="15">
-        <v>-55</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="I18" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J18" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K18" s="15">
-        <v>-37.5</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="L18" s="15">
-        <v>-33.333333333333</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="M18" s="15">
-        <v>-31.034482758620</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.189189189189</v>
+        <v>-89.090909090909</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D19" s="14">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>-25</v>
+        <v>87.5</v>
       </c>
       <c r="F19" s="14">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G19" s="14">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H19" s="15">
-        <v>8.333333333333</v>
+        <v>17.021276595744</v>
       </c>
       <c r="I19" s="14">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="J19" s="14">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="K19" s="15">
-        <v>28.571428571428</v>
+        <v>34.615384615384</v>
       </c>
       <c r="L19" s="15">
-        <v>-7.216494845360</v>
+        <v>-1.869158878504</v>
       </c>
       <c r="M19" s="15">
-        <v>80</v>
+        <v>77.966101694915</v>
       </c>
       <c r="N19" s="15">
-        <v>-10</v>
+        <v>-7.894736842105</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G20" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H20" s="15">
-        <v>50</v>
+        <v>-25</v>
       </c>
       <c r="I20" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J20" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K20" s="15">
-        <v>111.764705882353</v>
+        <v>100</v>
       </c>
       <c r="L20" s="15">
-        <v>100</v>
+        <v>122.222222222222</v>
       </c>
       <c r="M20" s="15">
-        <v>28.571428571428</v>
+        <v>21.212121212121</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.617100371747</v>
+        <v>-86.885245901639</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D21" s="17">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>-13.793103448275</v>
+        <v>55.555555555555</v>
       </c>
       <c r="F21" s="17">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="G21" s="17">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="H21" s="18">
-        <v>9.090909090909</v>
+        <v>11.764705882352</v>
       </c>
       <c r="I21" s="17">
-        <v>207</v>
+        <v>236</v>
       </c>
       <c r="J21" s="17">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="K21" s="18">
-        <v>23.214285714285</v>
+        <v>26.881720430107</v>
       </c>
       <c r="L21" s="18">
-        <v>1.470588235294</v>
+        <v>5.357142857142</v>
       </c>
       <c r="M21" s="18">
-        <v>31.847133757961</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.941176470588</v>
+        <v>-72.748267898383</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="14">
-        <v>3</v>
-      </c>
       <c r="E22" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>166.666666666667</v>
+        <v>75</v>
       </c>
       <c r="I22" s="14">
         <v>10</v>
       </c>
       <c r="J22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K22" s="15">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="L22" s="15">
-        <v>150</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M22" s="15">
-        <v>42.857142857142</v>
+        <v>25</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D24" s="14">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E24" s="15">
-        <v>138.888888888889</v>
+        <v>46.666666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G24" s="14">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="H24" s="15">
-        <v>15.887850467289</v>
+        <v>33.663366336633</v>
       </c>
       <c r="I24" s="14">
-        <v>196</v>
+        <v>239</v>
       </c>
       <c r="J24" s="14">
-        <v>197</v>
+        <v>227</v>
       </c>
       <c r="K24" s="15">
-        <v>-0.507614213197</v>
+        <v>5.286343612334</v>
       </c>
       <c r="L24" s="15">
-        <v>-25.757575757575</v>
+        <v>-22.149837133550</v>
       </c>
       <c r="M24" s="15">
-        <v>139.024390243902</v>
+        <v>139</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>35</v>
       </c>
       <c r="D25" s="14">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E25" s="15">
-        <v>337.5</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="G25" s="14">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H25" s="15">
-        <v>40</v>
+        <v>69.642857142857</v>
       </c>
       <c r="I25" s="14">
-        <v>119</v>
+        <v>152</v>
       </c>
       <c r="J25" s="14">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="K25" s="15">
-        <v>7.207207207207</v>
+        <v>15.151515151515</v>
       </c>
       <c r="L25" s="15">
-        <v>-25.157232704402</v>
+        <v>-19.148936170212</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D26" s="14">
         <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>11.111111111111</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F26" s="14">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G26" s="14">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H26" s="15">
-        <v>41.666666666666</v>
+        <v>10.344827586206</v>
       </c>
       <c r="I26" s="14">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="J26" s="14">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="K26" s="15">
-        <v>13.725490196078</v>
+        <v>5</v>
       </c>
       <c r="L26" s="15">
-        <v>-4.918032786885</v>
+        <v>-19.230769230769</v>
       </c>
       <c r="M26" s="15">
-        <v>-15.942028985507</v>
+        <v>-17.105263157894</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
         <v>7</v>
       </c>
       <c r="J27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K27" s="15">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="L27" s="15">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="14">
+        <v>2</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I28" s="14">
+        <v>7</v>
+      </c>
+      <c r="J28" s="14">
         <v>5</v>
       </c>
-      <c r="J28" s="14">
-        <v>3</v>
-      </c>
       <c r="K28" s="15">
-        <v>66.666666666666</v>
+        <v>40</v>
       </c>
       <c r="L28" s="15">
-        <v>-44.444444444444</v>
+        <v>-30</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1496,8 +1496,8 @@
       <c r="L29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M29" s="13" t="s">
-        <v>21</v>
+      <c r="M29" s="15">
+        <v>-100</v>
       </c>
       <c r="N29" s="15">
         <v>-100</v>
@@ -1537,8 +1537,8 @@
       <c r="L30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M30" s="13" t="s">
-        <v>21</v>
+      <c r="M30" s="15">
+        <v>-100</v>
       </c>
       <c r="N30" s="15">
         <v>-100</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1634,8 +1634,8 @@
       <c r="K33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L33" s="13" t="s">
-        <v>21</v>
+      <c r="L33" s="15">
+        <v>-100</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-108pct.xlsx
+++ b/data/source/weekly/cs-en-us-108pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="14">
+      <c r="C15" s="14">
         <v>1</v>
       </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J15" s="14">
         <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M15" s="15">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="N15" s="15">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>-25</v>
       </c>
       <c r="F16" s="14">
         <v>13</v>
       </c>
       <c r="G16" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H16" s="15">
+        <v>0</v>
+      </c>
+      <c r="I16" s="14">
+        <v>26</v>
+      </c>
+      <c r="J16" s="14">
+        <v>24</v>
+      </c>
+      <c r="K16" s="15">
         <v>8.333333333333</v>
       </c>
-      <c r="I16" s="14">
-        <v>23</v>
-      </c>
-      <c r="J16" s="14">
-        <v>20</v>
-      </c>
-      <c r="K16" s="15">
-        <v>15</v>
-      </c>
       <c r="L16" s="15">
-        <v>-28.125</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="M16" s="15">
-        <v>-32.352941176470</v>
+        <v>-29.729729729729</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.700534759358</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E17" s="15">
-        <v>33.333333333333</v>
+        <v>-60</v>
       </c>
       <c r="F17" s="14">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G17" s="14">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H17" s="15">
-        <v>85.714285714285</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J17" s="14">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="K17" s="15">
-        <v>31.034482758620</v>
+        <v>10.256410256410</v>
       </c>
       <c r="L17" s="15">
-        <v>11.764705882352</v>
+        <v>16.216216216216</v>
       </c>
       <c r="M17" s="15">
-        <v>153.333333333333</v>
+        <v>152.941176470588</v>
       </c>
       <c r="N17" s="15">
-        <v>2.702702702702</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F18" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G18" s="14">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H18" s="15">
-        <v>-35.714285714285</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="I18" s="14">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J18" s="14">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="K18" s="15">
-        <v>-29.411764705882</v>
+        <v>-26.829268292682</v>
       </c>
       <c r="L18" s="15">
-        <v>-27.272727272727</v>
+        <v>-26.829268292682</v>
       </c>
       <c r="M18" s="15">
-        <v>-29.411764705882</v>
+        <v>-25</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.090909090909</v>
+        <v>-87.755102040816</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E19" s="15">
-        <v>87.5</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="F19" s="14">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G19" s="14">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H19" s="15">
-        <v>17.021276595744</v>
+        <v>12</v>
       </c>
       <c r="I19" s="14">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="J19" s="14">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K19" s="15">
-        <v>34.615384615384</v>
+        <v>28.089887640449</v>
       </c>
       <c r="L19" s="15">
-        <v>-1.869158878504</v>
+        <v>-4.201680672268</v>
       </c>
       <c r="M19" s="15">
-        <v>77.966101694915</v>
+        <v>75.384615384615</v>
       </c>
       <c r="N19" s="15">
-        <v>-7.894736842105</v>
+        <v>-15.555555555555</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F20" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G20" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H20" s="15">
-        <v>-25</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I20" s="14">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J20" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K20" s="15">
-        <v>100</v>
+        <v>95.454545454545</v>
       </c>
       <c r="L20" s="15">
-        <v>122.222222222222</v>
+        <v>126.315789473684</v>
       </c>
       <c r="M20" s="15">
-        <v>21.212121212121</v>
+        <v>13.157894736842</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.885245901639</v>
+        <v>-87.125748502994</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E21" s="18">
-        <v>55.555555555555</v>
+        <v>-20.588235294117</v>
       </c>
       <c r="F21" s="17">
         <v>114</v>
       </c>
       <c r="G21" s="17">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="H21" s="18">
-        <v>11.764705882352</v>
+        <v>-2.564102564102</v>
       </c>
       <c r="I21" s="17">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="J21" s="17">
-        <v>186</v>
+        <v>220</v>
       </c>
       <c r="K21" s="18">
-        <v>26.881720430107</v>
+        <v>19.545454545454</v>
       </c>
       <c r="L21" s="18">
-        <v>5.357142857142</v>
+        <v>3.543307086614</v>
       </c>
       <c r="M21" s="18">
-        <v>33.333333333333</v>
+        <v>31.5</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.748267898383</v>
+        <v>-72.746113989637</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,28 +1189,28 @@
         <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H22" s="15">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14">
         <v>10</v>
       </c>
       <c r="J22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K22" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L22" s="15">
         <v>66.666666666666</v>
       </c>
       <c r="M22" s="15">
-        <v>25</v>
+        <v>11.111111111111</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D24" s="14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E24" s="15">
-        <v>46.666666666666</v>
+        <v>-2.941176470588</v>
       </c>
       <c r="F24" s="14">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="G24" s="14">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="H24" s="15">
-        <v>33.663366336633</v>
+        <v>33.035714285714</v>
       </c>
       <c r="I24" s="14">
-        <v>239</v>
+        <v>273</v>
       </c>
       <c r="J24" s="14">
-        <v>227</v>
+        <v>261</v>
       </c>
       <c r="K24" s="15">
-        <v>5.286343612334</v>
+        <v>4.597701149425</v>
       </c>
       <c r="L24" s="15">
-        <v>-22.149837133550</v>
+        <v>-24.166666666666</v>
       </c>
       <c r="M24" s="15">
-        <v>139</v>
+        <v>152.777777777778</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D25" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E25" s="15">
-        <v>66.666666666666</v>
+        <v>13.636363636363</v>
       </c>
       <c r="F25" s="14">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="G25" s="14">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="H25" s="15">
-        <v>69.642857142857</v>
+        <v>74.603174603174</v>
       </c>
       <c r="I25" s="14">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="J25" s="14">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="K25" s="15">
-        <v>15.151515151515</v>
+        <v>14.935064935064</v>
       </c>
       <c r="L25" s="15">
-        <v>-19.148936170212</v>
+        <v>-20.982142857142</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E26" s="15">
-        <v>-44.444444444444</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F26" s="14">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G26" s="14">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="H26" s="15">
-        <v>10.344827586206</v>
+        <v>-32.5</v>
       </c>
       <c r="I26" s="14">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="J26" s="14">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="K26" s="15">
-        <v>5</v>
+        <v>-10.256410256410</v>
       </c>
       <c r="L26" s="15">
-        <v>-19.230769230769</v>
+        <v>-23.913043478260</v>
       </c>
       <c r="M26" s="15">
-        <v>-17.105263157894</v>
+        <v>-19.540229885057</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="14">
+      <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
         <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J27" s="14">
         <v>5</v>
       </c>
       <c r="K27" s="15">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="L27" s="15">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="14">
         <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="14">
+        <v>8</v>
+      </c>
+      <c r="J28" s="14">
         <v>7</v>
       </c>
-      <c r="J28" s="14">
-        <v>5</v>
-      </c>
       <c r="K28" s="15">
-        <v>40</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L28" s="15">
-        <v>-30</v>
+        <v>-20</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1576,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-108pct.xlsx
+++ b/data/source/weekly/cs-en-us-108pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -892,23 +892,23 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="14">
-        <v>3</v>
-      </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
         <v>7</v>
@@ -919,8 +919,8 @@
       <c r="K15" s="15">
         <v>133.333333333333</v>
       </c>
-      <c r="L15" s="13" t="s">
-        <v>21</v>
+      <c r="L15" s="15">
+        <v>600</v>
       </c>
       <c r="M15" s="15">
         <v>250</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
         <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G16" s="14">
         <v>13</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="I16" s="14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J16" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K16" s="15">
-        <v>8.333333333333</v>
+        <v>7.142857142857</v>
       </c>
       <c r="L16" s="15">
-        <v>-31.578947368421</v>
+        <v>-30.232558139534</v>
       </c>
       <c r="M16" s="15">
-        <v>-29.729729729729</v>
+        <v>-26.829268292682</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.5</v>
+        <v>-86.899563318777</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -987,28 +987,28 @@
         <v>21</v>
       </c>
       <c r="G17" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H17" s="15">
+        <v>-16</v>
+      </c>
+      <c r="I17" s="14">
+        <v>49</v>
+      </c>
+      <c r="J17" s="14">
+        <v>49</v>
+      </c>
+      <c r="K17" s="15">
         <v>0</v>
       </c>
-      <c r="I17" s="14">
-        <v>43</v>
-      </c>
-      <c r="J17" s="14">
-        <v>39</v>
-      </c>
-      <c r="K17" s="15">
-        <v>10.256410256410</v>
-      </c>
       <c r="L17" s="15">
-        <v>16.216216216216</v>
+        <v>19.512195121951</v>
       </c>
       <c r="M17" s="15">
-        <v>152.941176470588</v>
+        <v>113.04347826087</v>
       </c>
       <c r="N17" s="15">
-        <v>7.5</v>
+        <v>13.953488372093</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-14.285714285714</v>
+        <v>-60</v>
       </c>
       <c r="F18" s="14">
         <v>13</v>
       </c>
       <c r="G18" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H18" s="15">
-        <v>-31.578947368421</v>
+        <v>-18.75</v>
       </c>
       <c r="I18" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J18" s="14">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="K18" s="15">
-        <v>-26.829268292682</v>
+        <v>-28.260869565217</v>
       </c>
       <c r="L18" s="15">
-        <v>-26.829268292682</v>
+        <v>-28.260869565217</v>
       </c>
       <c r="M18" s="15">
-        <v>-25</v>
+        <v>-29.787234042553</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.755102040816</v>
+        <v>-87.822878228782</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E19" s="15">
-        <v>-9.090909090909</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F19" s="14">
+        <v>49</v>
+      </c>
+      <c r="G19" s="14">
         <v>56</v>
       </c>
-      <c r="G19" s="14">
-        <v>50</v>
-      </c>
       <c r="H19" s="15">
-        <v>12</v>
+        <v>-12.5</v>
       </c>
       <c r="I19" s="14">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="J19" s="14">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="K19" s="15">
-        <v>28.089887640449</v>
+        <v>15.454545454545</v>
       </c>
       <c r="L19" s="15">
-        <v>-4.201680672268</v>
+        <v>-4.511278195488</v>
       </c>
       <c r="M19" s="15">
-        <v>75.384615384615</v>
+        <v>78.873239436619</v>
       </c>
       <c r="N19" s="15">
-        <v>-15.555555555555</v>
+        <v>-12.413793103448</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D20" s="14">
         <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F20" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G20" s="14">
         <v>11</v>
       </c>
       <c r="H20" s="15">
-        <v>-27.272727272727</v>
+        <v>18.181818181818</v>
       </c>
       <c r="I20" s="14">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J20" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K20" s="15">
-        <v>95.454545454545</v>
+        <v>104.166666666667</v>
       </c>
       <c r="L20" s="15">
-        <v>126.315789473684</v>
+        <v>122.727272727273</v>
       </c>
       <c r="M20" s="15">
-        <v>13.157894736842</v>
+        <v>16.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-87.125748502994</v>
+        <v>-86.575342465753</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,75 +1139,75 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D21" s="17">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E21" s="18">
-        <v>-20.588235294117</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F21" s="17">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="G21" s="17">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="H21" s="18">
-        <v>-2.564102564102</v>
+        <v>-11.382113821138</v>
       </c>
       <c r="I21" s="17">
-        <v>263</v>
+        <v>295</v>
       </c>
       <c r="J21" s="17">
-        <v>220</v>
+        <v>262</v>
       </c>
       <c r="K21" s="18">
-        <v>19.545454545454</v>
+        <v>12.595419847328</v>
       </c>
       <c r="L21" s="18">
-        <v>3.543307086614</v>
+        <v>3.146853146853</v>
       </c>
       <c r="M21" s="18">
-        <v>31.5</v>
+        <v>29.955947136563</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.746113989637</v>
+        <v>-72.090823084200</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E22" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F22" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H22" s="15">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="I22" s="14">
         <v>10</v>
       </c>
       <c r="J22" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K22" s="15">
-        <v>66.666666666666</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L22" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="M22" s="15">
         <v>11.111111111111</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D24" s="14">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E24" s="15">
-        <v>-2.941176470588</v>
+        <v>73.913043478260</v>
       </c>
       <c r="F24" s="14">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="G24" s="14">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="H24" s="15">
-        <v>33.035714285714</v>
+        <v>51.428571428571</v>
       </c>
       <c r="I24" s="14">
-        <v>273</v>
+        <v>312</v>
       </c>
       <c r="J24" s="14">
-        <v>261</v>
+        <v>284</v>
       </c>
       <c r="K24" s="15">
-        <v>4.597701149425</v>
+        <v>9.859154929577</v>
       </c>
       <c r="L24" s="15">
-        <v>-24.166666666666</v>
+        <v>-22.962962962963</v>
       </c>
       <c r="M24" s="15">
-        <v>152.777777777778</v>
+        <v>153.658536585366</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D25" s="14">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E25" s="15">
-        <v>13.636363636363</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G25" s="14">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H25" s="15">
-        <v>74.603174603174</v>
+        <v>62.121212121212</v>
       </c>
       <c r="I25" s="14">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="J25" s="14">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="K25" s="15">
-        <v>14.935064935064</v>
+        <v>12.426035502958</v>
       </c>
       <c r="L25" s="15">
-        <v>-20.982142857142</v>
+        <v>-26.356589147286</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>8</v>
       </c>
       <c r="D26" s="14">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>-55.555555555555</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G26" s="14">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="H26" s="15">
-        <v>-32.5</v>
+        <v>-35.416666666666</v>
       </c>
       <c r="I26" s="14">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="J26" s="14">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K26" s="15">
-        <v>-10.256410256410</v>
+        <v>-14.444444444444</v>
       </c>
       <c r="L26" s="15">
-        <v>-23.913043478260</v>
+        <v>-27.358490566037</v>
       </c>
       <c r="M26" s="15">
-        <v>-19.540229885057</v>
+        <v>-18.947368421052</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J27" s="14">
         <v>5</v>
       </c>
       <c r="K27" s="15">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="L27" s="15">
-        <v>300</v>
+        <v>125</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
       <c r="E28" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>-33.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="I28" s="14">
+        <v>9</v>
+      </c>
+      <c r="J28" s="14">
         <v>8</v>
       </c>
-      <c r="J28" s="14">
-        <v>7</v>
-      </c>
       <c r="K28" s="15">
-        <v>14.285714285714</v>
+        <v>12.5</v>
       </c>
       <c r="L28" s="15">
-        <v>-20</v>
+        <v>-10</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1576,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-108pct.xlsx
+++ b/data/source/weekly/cs-en-us-108pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
@@ -920,7 +920,7 @@
         <v>133.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="M15" s="15">
         <v>250</v>
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
         <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="F16" s="14">
         <v>12</v>
@@ -952,63 +952,63 @@
         <v>-7.692307692307</v>
       </c>
       <c r="I16" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J16" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K16" s="15">
-        <v>7.142857142857</v>
+        <v>3.125</v>
       </c>
       <c r="L16" s="15">
-        <v>-30.232558139534</v>
+        <v>-32.653061224489</v>
       </c>
       <c r="M16" s="15">
-        <v>-26.829268292682</v>
+        <v>-25</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.899563318777</v>
+        <v>-87.15953307393</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="14">
         <v>4</v>
       </c>
-      <c r="D17" s="14">
-        <v>10</v>
-      </c>
       <c r="E17" s="15">
-        <v>-60</v>
+        <v>-100</v>
       </c>
       <c r="F17" s="14">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G17" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H17" s="15">
-        <v>-16</v>
+        <v>-51.851851851851</v>
       </c>
       <c r="I17" s="14">
         <v>49</v>
       </c>
       <c r="J17" s="14">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K17" s="15">
-        <v>0</v>
+        <v>-7.547169811320</v>
       </c>
       <c r="L17" s="15">
-        <v>19.512195121951</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M17" s="15">
-        <v>113.04347826087</v>
+        <v>88.461538461538</v>
       </c>
       <c r="N17" s="15">
-        <v>13.953488372093</v>
+        <v>2.083333333333</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D18" s="14">
         <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-60</v>
+        <v>40</v>
       </c>
       <c r="F18" s="14">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G18" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H18" s="15">
-        <v>-18.75</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="I18" s="14">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="J18" s="14">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="K18" s="15">
-        <v>-28.260869565217</v>
+        <v>-21.568627450980</v>
       </c>
       <c r="L18" s="15">
-        <v>-28.260869565217</v>
+        <v>-25.925925925925</v>
       </c>
       <c r="M18" s="15">
-        <v>-29.787234042553</v>
+        <v>-21.568627450980</v>
       </c>
       <c r="N18" s="15">
-        <v>-87.822878228782</v>
+        <v>-86.254295532646</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D19" s="14">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E19" s="15">
-        <v>-33.333333333333</v>
+        <v>220</v>
       </c>
       <c r="F19" s="14">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G19" s="14">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="H19" s="15">
-        <v>-12.5</v>
+        <v>15.555555555555</v>
       </c>
       <c r="I19" s="14">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="J19" s="14">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="K19" s="15">
-        <v>15.454545454545</v>
+        <v>22.608695652173</v>
       </c>
       <c r="L19" s="15">
-        <v>-4.511278195488</v>
+        <v>-0.704225352112</v>
       </c>
       <c r="M19" s="15">
-        <v>78.873239436619</v>
+        <v>76.25</v>
       </c>
       <c r="N19" s="15">
-        <v>-12.413793103448</v>
+        <v>-5.369127516778</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D20" s="14">
         <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F20" s="14">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G20" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H20" s="15">
-        <v>18.181818181818</v>
+        <v>122.222222222222</v>
       </c>
       <c r="I20" s="14">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="J20" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K20" s="15">
-        <v>104.166666666667</v>
+        <v>119.230769230769</v>
       </c>
       <c r="L20" s="15">
-        <v>122.727272727273</v>
+        <v>103.571428571429</v>
       </c>
       <c r="M20" s="15">
-        <v>16.666666666666</v>
+        <v>21.276595744680</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.575342465753</v>
+        <v>-85.532994923857</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D21" s="17">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>-28.571428571428</v>
+        <v>70</v>
       </c>
       <c r="F21" s="17">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="G21" s="17">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="H21" s="18">
-        <v>-11.382113821138</v>
+        <v>1.754385964912</v>
       </c>
       <c r="I21" s="17">
-        <v>295</v>
+        <v>327</v>
       </c>
       <c r="J21" s="17">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="K21" s="18">
-        <v>12.595419847328</v>
+        <v>15.957446808510</v>
       </c>
       <c r="L21" s="18">
-        <v>3.146853146853</v>
+        <v>3.154574132492</v>
       </c>
       <c r="M21" s="18">
-        <v>29.955947136563</v>
+        <v>29.761904761904</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.090823084200</v>
+        <v>-71.391076115485</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="14">
         <v>3</v>
       </c>
       <c r="E22" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" s="14">
         <v>8</v>
       </c>
       <c r="H22" s="15">
-        <v>-75</v>
+        <v>-62.5</v>
       </c>
       <c r="I22" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J22" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K22" s="15">
-        <v>11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="L22" s="15">
-        <v>25</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>11.111111111111</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="D24" s="14">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E24" s="15">
-        <v>73.913043478260</v>
+        <v>-32.352941176470</v>
       </c>
       <c r="F24" s="14">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="G24" s="14">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="H24" s="15">
-        <v>51.428571428571</v>
+        <v>17.355371900826</v>
       </c>
       <c r="I24" s="14">
-        <v>312</v>
+        <v>337</v>
       </c>
       <c r="J24" s="14">
-        <v>284</v>
+        <v>318</v>
       </c>
       <c r="K24" s="15">
-        <v>9.859154929577</v>
+        <v>5.974842767295</v>
       </c>
       <c r="L24" s="15">
-        <v>-22.962962962963</v>
+        <v>-21.445221445221</v>
       </c>
       <c r="M24" s="15">
-        <v>153.658536585366</v>
+        <v>137.323943661972</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D25" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E25" s="15">
-        <v>-6.666666666666</v>
+        <v>-47.368421052631</v>
       </c>
       <c r="F25" s="14">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="G25" s="14">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H25" s="15">
-        <v>62.121212121212</v>
+        <v>9.090909090909</v>
       </c>
       <c r="I25" s="14">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="J25" s="14">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="K25" s="15">
-        <v>12.426035502958</v>
+        <v>6.382978723404</v>
       </c>
       <c r="L25" s="15">
-        <v>-26.356589147286</v>
+        <v>-26.470588235294</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E26" s="15">
-        <v>-33.333333333333</v>
+        <v>57.142857142857</v>
       </c>
       <c r="F26" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G26" s="14">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H26" s="15">
-        <v>-35.416666666666</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="I26" s="14">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J26" s="14">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="K26" s="15">
-        <v>-14.444444444444</v>
+        <v>-9.278350515463</v>
       </c>
       <c r="L26" s="15">
-        <v>-27.358490566037</v>
+        <v>-26.050420168067</v>
       </c>
       <c r="M26" s="15">
-        <v>-18.947368421052</v>
+        <v>-14.563106796116</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1412,7 +1412,7 @@
         <v>80</v>
       </c>
       <c r="L27" s="15">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>1</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>-40</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="14">
+        <v>10</v>
+      </c>
+      <c r="J28" s="14">
         <v>9</v>
       </c>
-      <c r="J28" s="14">
-        <v>8</v>
-      </c>
       <c r="K28" s="15">
-        <v>12.5</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L28" s="15">
-        <v>-10</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1567,7 +1567,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="15">
-        <v>-80</v>
+        <v>-60</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-108pct.xlsx
+++ b/data/source/weekly/cs-en-us-108pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -904,29 +904,29 @@
       <c r="F15" s="14">
         <v>1</v>
       </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
-      <c r="H15" s="15">
-        <v>0</v>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J15" s="14">
         <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>133.333333333333</v>
+        <v>100</v>
       </c>
       <c r="L15" s="15">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="M15" s="15">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="N15" s="15">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,81 +934,81 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
         <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="F16" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G16" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H16" s="15">
-        <v>-7.692307692307</v>
+        <v>-6.25</v>
       </c>
       <c r="I16" s="14">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J16" s="14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K16" s="15">
-        <v>3.125</v>
+        <v>5.555555555555</v>
       </c>
       <c r="L16" s="15">
-        <v>-32.653061224489</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="M16" s="15">
-        <v>-25</v>
+        <v>-15.555555555555</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.15953307393</v>
+        <v>-86.619718309859</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>20</v>
+      <c r="C17" s="14">
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E17" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G17" s="14">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H17" s="15">
-        <v>-51.851851851851</v>
+        <v>-46.875</v>
       </c>
       <c r="I17" s="14">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="J17" s="14">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="K17" s="15">
-        <v>-7.547169811320</v>
+        <v>-6.557377049180</v>
       </c>
       <c r="L17" s="15">
-        <v>16.666666666666</v>
+        <v>21.276595744680</v>
       </c>
       <c r="M17" s="15">
-        <v>88.461538461538</v>
+        <v>103.571428571429</v>
       </c>
       <c r="N17" s="15">
-        <v>2.083333333333</v>
+        <v>1.785714285714</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>40</v>
+        <v>-25</v>
       </c>
       <c r="F18" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G18" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H18" s="15">
-        <v>-5.263157894736</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="I18" s="14">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J18" s="14">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K18" s="15">
-        <v>-21.568627450980</v>
+        <v>-21.818181818181</v>
       </c>
       <c r="L18" s="15">
-        <v>-25.925925925925</v>
+        <v>-25.862068965517</v>
       </c>
       <c r="M18" s="15">
-        <v>-21.568627450980</v>
+        <v>-24.561403508771</v>
       </c>
       <c r="N18" s="15">
-        <v>-86.254295532646</v>
+        <v>-86.173633440514</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D19" s="14">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E19" s="15">
-        <v>220</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F19" s="14">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G19" s="14">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H19" s="15">
-        <v>15.555555555555</v>
+        <v>-1.818181818181</v>
       </c>
       <c r="I19" s="14">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="J19" s="14">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="K19" s="15">
-        <v>22.608695652173</v>
+        <v>17.293233082706</v>
       </c>
       <c r="L19" s="15">
-        <v>-0.704225352112</v>
+        <v>-3.105590062111</v>
       </c>
       <c r="M19" s="15">
-        <v>76.25</v>
+        <v>75.280898876404</v>
       </c>
       <c r="N19" s="15">
-        <v>-5.369127516778</v>
+        <v>-6.586826347305</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F20" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G20" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H20" s="15">
-        <v>122.222222222222</v>
+        <v>228.571428571429</v>
       </c>
       <c r="I20" s="14">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="J20" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K20" s="15">
-        <v>119.230769230769</v>
+        <v>133.333333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>103.571428571429</v>
+        <v>85.294117647058</v>
       </c>
       <c r="M20" s="15">
-        <v>21.276595744680</v>
+        <v>18.867924528301</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.532994923857</v>
+        <v>-85.211267605633</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E21" s="18">
-        <v>70</v>
+        <v>5.714285714285</v>
       </c>
       <c r="F21" s="17">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="G21" s="17">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="H21" s="18">
-        <v>1.754385964912</v>
+        <v>-3.053435114503</v>
       </c>
       <c r="I21" s="17">
-        <v>327</v>
+        <v>363</v>
       </c>
       <c r="J21" s="17">
-        <v>282</v>
+        <v>317</v>
       </c>
       <c r="K21" s="18">
-        <v>15.957446808510</v>
+        <v>14.511041009463</v>
       </c>
       <c r="L21" s="18">
-        <v>3.154574132492</v>
+        <v>2.542372881355</v>
       </c>
       <c r="M21" s="18">
-        <v>29.761904761904</v>
+        <v>31.046931407942</v>
       </c>
       <c r="N21" s="18">
-        <v>-71.391076115485</v>
+        <v>-70.913461538461</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,34 +1180,34 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E22" s="15">
-        <v>-33.333333333333</v>
+        <v>-75</v>
       </c>
       <c r="F22" s="14">
         <v>3</v>
       </c>
       <c r="G22" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H22" s="15">
-        <v>-62.5</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="I22" s="14">
         <v>12</v>
       </c>
       <c r="J22" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="L22" s="15">
-        <v>33.333333333333</v>
+        <v>20</v>
       </c>
       <c r="M22" s="15">
         <v>33.333333333333</v>
@@ -1265,34 +1265,34 @@
         <v>23</v>
       </c>
       <c r="D24" s="14">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E24" s="15">
-        <v>-32.352941176470</v>
+        <v>9.523809523809</v>
       </c>
       <c r="F24" s="14">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="G24" s="14">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="H24" s="15">
-        <v>17.355371900826</v>
+        <v>7.142857142857</v>
       </c>
       <c r="I24" s="14">
-        <v>337</v>
+        <v>360</v>
       </c>
       <c r="J24" s="14">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="K24" s="15">
-        <v>5.974842767295</v>
+        <v>6.194690265486</v>
       </c>
       <c r="L24" s="15">
-        <v>-21.445221445221</v>
+        <v>-24.843423799582</v>
       </c>
       <c r="M24" s="15">
-        <v>137.323943661972</v>
+        <v>122.222222222222</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D25" s="14">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E25" s="15">
-        <v>-47.368421052631</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="G25" s="14">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="H25" s="15">
-        <v>9.090909090909</v>
+        <v>-16.176470588235</v>
       </c>
       <c r="I25" s="14">
+        <v>208</v>
+      </c>
+      <c r="J25" s="14">
         <v>200</v>
       </c>
-      <c r="J25" s="14">
-        <v>188</v>
-      </c>
       <c r="K25" s="15">
-        <v>6.382978723404</v>
+        <v>4</v>
       </c>
       <c r="L25" s="15">
-        <v>-26.470588235294</v>
+        <v>-33.118971061093</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>57.142857142857</v>
+        <v>10</v>
       </c>
       <c r="F26" s="14">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G26" s="14">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H26" s="15">
-        <v>-30.434782608695</v>
+        <v>-14.893617021276</v>
       </c>
       <c r="I26" s="14">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="J26" s="14">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="K26" s="15">
-        <v>-9.278350515463</v>
+        <v>-5.607476635514</v>
       </c>
       <c r="L26" s="15">
-        <v>-26.050420168067</v>
+        <v>-22.900763358778</v>
       </c>
       <c r="M26" s="15">
-        <v>-14.563106796116</v>
+        <v>-13.675213675213</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,11 +1387,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
@@ -1403,16 +1403,16 @@
         <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K27" s="15">
-        <v>80</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
         <v>4</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>-33.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="I28" s="14">
+        <v>12</v>
+      </c>
+      <c r="J28" s="14">
         <v>10</v>
       </c>
-      <c r="J28" s="14">
-        <v>9</v>
-      </c>
       <c r="K28" s="15">
-        <v>11.111111111111</v>
+        <v>20</v>
       </c>
       <c r="L28" s="15">
-        <v>-23.076923076923</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-108pct.xlsx
+++ b/data/source/weekly/cs-en-us-108pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -895,38 +895,38 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="14">
+      <c r="D15" s="14">
         <v>1</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+      <c r="E15" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15">
+        <v>-100</v>
       </c>
       <c r="I15" s="14">
         <v>6</v>
       </c>
       <c r="J15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L15" s="15">
         <v>200</v>
       </c>
       <c r="M15" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N15" s="15">
-        <v>500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -943,31 +943,31 @@
         <v>25</v>
       </c>
       <c r="F16" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G16" s="14">
         <v>16</v>
       </c>
       <c r="H16" s="15">
-        <v>-6.25</v>
+        <v>6.25</v>
       </c>
       <c r="I16" s="14">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J16" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K16" s="15">
-        <v>5.555555555555</v>
+        <v>7.5</v>
       </c>
       <c r="L16" s="15">
-        <v>-26.923076923076</v>
+        <v>-24.561403508771</v>
       </c>
       <c r="M16" s="15">
-        <v>-15.555555555555</v>
+        <v>-8.510638297872</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.619718309859</v>
+        <v>-85.521885521885</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="F17" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G17" s="14">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="H17" s="15">
-        <v>-46.875</v>
+        <v>-48.148148148148</v>
       </c>
       <c r="I17" s="14">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J17" s="14">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="K17" s="15">
-        <v>-6.557377049180</v>
+        <v>-10.606060606060</v>
       </c>
       <c r="L17" s="15">
-        <v>21.276595744680</v>
+        <v>18</v>
       </c>
       <c r="M17" s="15">
-        <v>103.571428571429</v>
+        <v>90.322580645161</v>
       </c>
       <c r="N17" s="15">
-        <v>1.785714285714</v>
+        <v>-4.838709677419</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>5</v>
+      </c>
+      <c r="D18" s="14">
         <v>3</v>
       </c>
-      <c r="D18" s="14">
-        <v>4</v>
-      </c>
       <c r="E18" s="15">
-        <v>-25</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F18" s="14">
         <v>17</v>
       </c>
       <c r="G18" s="14">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H18" s="15">
-        <v>-19.047619047619</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J18" s="14">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K18" s="15">
-        <v>-21.818181818181</v>
+        <v>-17.241379310344</v>
       </c>
       <c r="L18" s="15">
-        <v>-25.862068965517</v>
+        <v>-22.580645161290</v>
       </c>
       <c r="M18" s="15">
-        <v>-24.561403508771</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="N18" s="15">
-        <v>-86.173633440514</v>
+        <v>-85.756676557863</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D19" s="14">
         <v>18</v>
       </c>
       <c r="E19" s="15">
-        <v>-16.666666666666</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="F19" s="14">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G19" s="14">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="H19" s="15">
-        <v>-1.818181818181</v>
+        <v>-9.677419354838</v>
       </c>
       <c r="I19" s="14">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="J19" s="14">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="K19" s="15">
-        <v>17.293233082706</v>
+        <v>11.258278145695</v>
       </c>
       <c r="L19" s="15">
-        <v>-3.105590062111</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="M19" s="15">
-        <v>75.280898876404</v>
+        <v>63.106796116504</v>
       </c>
       <c r="N19" s="15">
-        <v>-6.586826347305</v>
+        <v>-5.617977528089</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
         <v>23</v>
       </c>
       <c r="G20" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H20" s="15">
-        <v>228.571428571429</v>
+        <v>155.555555555556</v>
       </c>
       <c r="I20" s="14">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J20" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K20" s="15">
-        <v>133.333333333333</v>
+        <v>112.903225806452</v>
       </c>
       <c r="L20" s="15">
-        <v>85.294117647058</v>
+        <v>73.684210526315</v>
       </c>
       <c r="M20" s="15">
-        <v>18.867924528301</v>
+        <v>17.857142857142</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.211267605633</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D21" s="17">
         <v>35</v>
       </c>
       <c r="E21" s="18">
-        <v>5.714285714285</v>
+        <v>-17.142857142857</v>
       </c>
       <c r="F21" s="17">
         <v>127</v>
       </c>
       <c r="G21" s="17">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H21" s="18">
-        <v>-3.053435114503</v>
+        <v>-3.787878787878</v>
       </c>
       <c r="I21" s="17">
-        <v>363</v>
+        <v>390</v>
       </c>
       <c r="J21" s="17">
-        <v>317</v>
+        <v>352</v>
       </c>
       <c r="K21" s="18">
-        <v>14.511041009463</v>
+        <v>10.795454545454</v>
       </c>
       <c r="L21" s="18">
-        <v>2.542372881355</v>
+        <v>0.257069408740</v>
       </c>
       <c r="M21" s="18">
-        <v>31.046931407942</v>
+        <v>26.213592233009</v>
       </c>
       <c r="N21" s="18">
-        <v>-70.913461538461</v>
+        <v>-70.960536113179</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="14">
         <v>4</v>
       </c>
       <c r="E22" s="15">
-        <v>-75</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>3</v>
       </c>
       <c r="G22" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H22" s="15">
-        <v>-72.727272727272</v>
+        <v>-78.571428571428</v>
       </c>
       <c r="I22" s="14">
         <v>12</v>
       </c>
       <c r="J22" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K22" s="15">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="L22" s="15">
         <v>20</v>
       </c>
       <c r="M22" s="15">
-        <v>33.333333333333</v>
+        <v>20</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1265,34 +1265,34 @@
         <v>23</v>
       </c>
       <c r="D24" s="14">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E24" s="15">
-        <v>9.523809523809</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="F24" s="14">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="G24" s="14">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="H24" s="15">
-        <v>7.142857142857</v>
+        <v>3.773584905660</v>
       </c>
       <c r="I24" s="14">
-        <v>360</v>
+        <v>383</v>
       </c>
       <c r="J24" s="14">
-        <v>339</v>
+        <v>367</v>
       </c>
       <c r="K24" s="15">
-        <v>6.194690265486</v>
+        <v>4.359673024523</v>
       </c>
       <c r="L24" s="15">
-        <v>-24.843423799582</v>
+        <v>-26.346153846153</v>
       </c>
       <c r="M24" s="15">
-        <v>122.222222222222</v>
+        <v>112.777777777778</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D25" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E25" s="15">
-        <v>-33.333333333333</v>
+        <v>-56.25</v>
       </c>
       <c r="F25" s="14">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="G25" s="14">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="H25" s="15">
-        <v>-16.176470588235</v>
+        <v>-33.870967741935</v>
       </c>
       <c r="I25" s="14">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="J25" s="14">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="K25" s="15">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L25" s="15">
-        <v>-33.118971061093</v>
+        <v>-37.209302325581</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E26" s="15">
-        <v>10</v>
+        <v>-50</v>
       </c>
       <c r="F26" s="14">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G26" s="14">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H26" s="15">
-        <v>-14.893617021276</v>
+        <v>-9.302325581395</v>
       </c>
       <c r="I26" s="14">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="J26" s="14">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="K26" s="15">
-        <v>-5.607476635514</v>
+        <v>-10.743801652892</v>
       </c>
       <c r="L26" s="15">
-        <v>-22.900763358778</v>
+        <v>-24.475524475524</v>
       </c>
       <c r="M26" s="15">
-        <v>-13.675213675213</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,22 +1394,22 @@
         <v>-100</v>
       </c>
       <c r="F27" s="14">
+        <v>1</v>
+      </c>
+      <c r="G27" s="14">
         <v>2</v>
       </c>
-      <c r="G27" s="14">
-        <v>1</v>
-      </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
         <v>8</v>
       </c>
       <c r="J27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>33.333333333333</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L27" s="15">
         <v>60</v>
@@ -1429,31 +1429,31 @@
         <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>-20</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J28" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K28" s="15">
-        <v>20</v>
+        <v>7.692307692307</v>
       </c>
       <c r="L28" s="15">
-        <v>-14.285714285714</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1625,8 +1625,8 @@
       <c r="H33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I33" s="13" t="s">
-        <v>20</v>
+      <c r="I33" s="14">
+        <v>1</v>
       </c>
       <c r="J33" s="13" t="s">
         <v>20</v>
@@ -1635,7 +1635,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-108pct.xlsx
+++ b/data/source/weekly/cs-en-us-108pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
@@ -923,7 +923,7 @@
         <v>200</v>
       </c>
       <c r="M15" s="15">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="N15" s="15">
         <v>200</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="F16" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G16" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H16" s="15">
-        <v>6.25</v>
+        <v>26.666666666666</v>
       </c>
       <c r="I16" s="14">
+        <v>49</v>
+      </c>
+      <c r="J16" s="14">
         <v>43</v>
       </c>
-      <c r="J16" s="14">
-        <v>40</v>
-      </c>
       <c r="K16" s="15">
-        <v>7.5</v>
+        <v>13.953488372093</v>
       </c>
       <c r="L16" s="15">
-        <v>-24.561403508771</v>
+        <v>-20.967741935483</v>
       </c>
       <c r="M16" s="15">
-        <v>-8.510638297872</v>
+        <v>-3.921568627450</v>
       </c>
       <c r="N16" s="15">
-        <v>-85.521885521885</v>
+        <v>-84.444444444444</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E17" s="15">
-        <v>-60</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="F17" s="14">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G17" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H17" s="15">
-        <v>-48.148148148148</v>
+        <v>-36.666666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="J17" s="14">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K17" s="15">
-        <v>-10.606060606060</v>
+        <v>-13.924050632911</v>
       </c>
       <c r="L17" s="15">
-        <v>18</v>
+        <v>21.428571428571</v>
       </c>
       <c r="M17" s="15">
-        <v>90.322580645161</v>
+        <v>112.5</v>
       </c>
       <c r="N17" s="15">
-        <v>-4.838709677419</v>
+        <v>7.936507936507</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
         <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G18" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I18" s="14">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J18" s="14">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K18" s="15">
-        <v>-17.241379310344</v>
+        <v>-16.393442622950</v>
       </c>
       <c r="L18" s="15">
-        <v>-22.580645161290</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="M18" s="15">
-        <v>-27.272727272727</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="N18" s="15">
-        <v>-85.756676557863</v>
+        <v>-86.103542234332</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>13</v>
       </c>
       <c r="D19" s="14">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E19" s="15">
-        <v>-27.777777777777</v>
+        <v>8.333333333333</v>
       </c>
       <c r="F19" s="14">
         <v>56</v>
       </c>
       <c r="G19" s="14">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="H19" s="15">
-        <v>-9.677419354838</v>
+        <v>5.660377358490</v>
       </c>
       <c r="I19" s="14">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="J19" s="14">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="K19" s="15">
-        <v>11.258278145695</v>
+        <v>11.042944785276</v>
       </c>
       <c r="L19" s="15">
-        <v>-6.666666666666</v>
+        <v>-5.235602094240</v>
       </c>
       <c r="M19" s="15">
-        <v>63.106796116504</v>
+        <v>63.063063063063</v>
       </c>
       <c r="N19" s="15">
-        <v>-5.617977528089</v>
+        <v>-6.701030927835</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
         <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G20" s="14">
         <v>9</v>
       </c>
       <c r="H20" s="15">
-        <v>155.555555555556</v>
+        <v>111.111111111111</v>
       </c>
       <c r="I20" s="14">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J20" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K20" s="15">
-        <v>112.903225806452</v>
+        <v>106.060606060606</v>
       </c>
       <c r="L20" s="15">
-        <v>73.684210526315</v>
+        <v>61.904761904761</v>
       </c>
       <c r="M20" s="15">
-        <v>17.857142857142</v>
+        <v>13.333333333333</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.714285714285</v>
+        <v>-86.290322580645</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D21" s="17">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E21" s="18">
-        <v>-17.142857142857</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G21" s="17">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="H21" s="18">
-        <v>-3.787878787878</v>
+        <v>6.504065040650</v>
       </c>
       <c r="I21" s="17">
-        <v>390</v>
+        <v>423</v>
       </c>
       <c r="J21" s="17">
-        <v>352</v>
+        <v>385</v>
       </c>
       <c r="K21" s="18">
-        <v>10.795454545454</v>
+        <v>9.870129870129</v>
       </c>
       <c r="L21" s="18">
-        <v>0.257069408740</v>
+        <v>0.954653937947</v>
       </c>
       <c r="M21" s="18">
-        <v>26.213592233009</v>
+        <v>27.027027027027</v>
       </c>
       <c r="N21" s="18">
-        <v>-70.960536113179</v>
+        <v>-70.665742024965</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,34 +1183,34 @@
         <v>20</v>
       </c>
       <c r="D22" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E22" s="15">
         <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H22" s="15">
-        <v>-78.571428571428</v>
+        <v>-84.615384615384</v>
       </c>
       <c r="I22" s="14">
         <v>12</v>
       </c>
       <c r="J22" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K22" s="15">
-        <v>-40</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="L22" s="15">
-        <v>20</v>
+        <v>9.090909090909</v>
       </c>
       <c r="M22" s="15">
-        <v>20</v>
+        <v>9.090909090909</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D24" s="14">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E24" s="15">
-        <v>-17.857142857142</v>
+        <v>-61.764705882352</v>
       </c>
       <c r="F24" s="14">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="G24" s="14">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="H24" s="15">
-        <v>3.773584905660</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="I24" s="14">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="J24" s="14">
-        <v>367</v>
+        <v>401</v>
       </c>
       <c r="K24" s="15">
-        <v>4.359673024523</v>
+        <v>-1.246882793017</v>
       </c>
       <c r="L24" s="15">
-        <v>-26.346153846153</v>
+        <v>-29.787234042553</v>
       </c>
       <c r="M24" s="15">
-        <v>112.777777777778</v>
+        <v>97.014925373134</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E25" s="15">
-        <v>-56.25</v>
+        <v>-80</v>
       </c>
       <c r="F25" s="14">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="G25" s="14">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H25" s="15">
-        <v>-33.870967741935</v>
+        <v>-55.223880597014</v>
       </c>
       <c r="I25" s="14">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="J25" s="14">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="K25" s="15">
-        <v>0</v>
+        <v>-6.779661016949</v>
       </c>
       <c r="L25" s="15">
-        <v>-37.209302325581</v>
+        <v>-41.489361702127</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G26" s="14">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H26" s="15">
-        <v>-9.302325581395</v>
+        <v>2.380952380952</v>
       </c>
       <c r="I26" s="14">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="J26" s="14">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="K26" s="15">
-        <v>-10.743801652892</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="L26" s="15">
-        <v>-24.475524475524</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M26" s="15">
-        <v>-14.285714285714</v>
+        <v>-9.774436090225</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,20 +1387,20 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="14">
-        <v>1</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I27" s="14">
         <v>8</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" s="14">
         <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H28" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J28" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K28" s="15">
-        <v>7.692307692307</v>
+        <v>6.25</v>
       </c>
       <c r="L28" s="15">
-        <v>-6.666666666666</v>
+        <v>13.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1617,7 +1617,7 @@
         <v>21</v>
       </c>
       <c r="F33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1626,7 +1626,7 @@
         <v>21</v>
       </c>
       <c r="I33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" s="13" t="s">
         <v>20</v>
@@ -1635,7 +1635,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-108pct.xlsx
+++ b/data/source/weekly/cs-en-us-108pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -901,32 +901,32 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="F15" s="14">
+        <v>1</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J15" s="14">
         <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="L15" s="15">
-        <v>200</v>
+        <v>133.333333333333</v>
       </c>
       <c r="M15" s="15">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="N15" s="15">
-        <v>200</v>
+        <v>250</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G16" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H16" s="15">
-        <v>26.666666666666</v>
+        <v>27.777777777777</v>
       </c>
       <c r="I16" s="14">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="J16" s="14">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="K16" s="15">
-        <v>13.953488372093</v>
+        <v>12</v>
       </c>
       <c r="L16" s="15">
-        <v>-20.967741935483</v>
+        <v>-9.677419354838</v>
       </c>
       <c r="M16" s="15">
-        <v>-3.921568627450</v>
+        <v>3.703703703703</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.444444444444</v>
+        <v>-82.769230769230</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>-30.769230769230</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G17" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H17" s="15">
-        <v>-36.666666666666</v>
+        <v>-34.375</v>
       </c>
       <c r="I17" s="14">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J17" s="14">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="K17" s="15">
-        <v>-13.924050632911</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="L17" s="15">
-        <v>21.428571428571</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M17" s="15">
-        <v>112.5</v>
+        <v>100</v>
       </c>
       <c r="N17" s="15">
-        <v>7.936507936507</v>
+        <v>6.060606060606</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
+        <v>-25</v>
+      </c>
+      <c r="F18" s="14">
+        <v>14</v>
+      </c>
+      <c r="G18" s="14">
+        <v>14</v>
+      </c>
+      <c r="H18" s="15">
         <v>0</v>
       </c>
-      <c r="F18" s="14">
-        <v>18</v>
-      </c>
-      <c r="G18" s="14">
-        <v>15</v>
-      </c>
-      <c r="H18" s="15">
-        <v>20</v>
-      </c>
       <c r="I18" s="14">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J18" s="14">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="K18" s="15">
-        <v>-16.393442622950</v>
+        <v>-16.923076923076</v>
       </c>
       <c r="L18" s="15">
-        <v>-22.727272727272</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="M18" s="15">
-        <v>-29.166666666666</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="N18" s="15">
-        <v>-86.103542234332</v>
+        <v>-86.533665835411</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E19" s="15">
-        <v>8.333333333333</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G19" s="14">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="H19" s="15">
-        <v>5.660377358490</v>
+        <v>-26.984126984127</v>
       </c>
       <c r="I19" s="14">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="J19" s="14">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="K19" s="15">
-        <v>11.042944785276</v>
+        <v>5.617977528089</v>
       </c>
       <c r="L19" s="15">
-        <v>-5.235602094240</v>
+        <v>-5.050505050505</v>
       </c>
       <c r="M19" s="15">
-        <v>63.063063063063</v>
+        <v>56.666666666666</v>
       </c>
       <c r="N19" s="15">
-        <v>-6.701030927835</v>
+        <v>-7.389162561576</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F20" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G20" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H20" s="15">
-        <v>111.111111111111</v>
+        <v>41.666666666666</v>
       </c>
       <c r="I20" s="14">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="J20" s="14">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="K20" s="15">
-        <v>106.060606060606</v>
+        <v>94.736842105263</v>
       </c>
       <c r="L20" s="15">
-        <v>61.904761904761</v>
+        <v>57.446808510638</v>
       </c>
       <c r="M20" s="15">
-        <v>13.333333333333</v>
+        <v>15.625</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.290322580645</v>
+        <v>-86.168224299065</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D21" s="17">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>-29.729729729729</v>
       </c>
       <c r="F21" s="17">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="G21" s="17">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="H21" s="18">
-        <v>6.504065040650</v>
+        <v>-12.857142857142</v>
       </c>
       <c r="I21" s="17">
-        <v>423</v>
+        <v>449</v>
       </c>
       <c r="J21" s="17">
-        <v>385</v>
+        <v>422</v>
       </c>
       <c r="K21" s="18">
-        <v>9.870129870129</v>
+        <v>6.398104265402</v>
       </c>
       <c r="L21" s="18">
-        <v>0.954653937947</v>
+        <v>2.277904328018</v>
       </c>
       <c r="M21" s="18">
-        <v>27.027027027027</v>
+        <v>25.418994413407</v>
       </c>
       <c r="N21" s="18">
-        <v>-70.665742024965</v>
+        <v>-70.787247885491</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,28 +1183,28 @@
         <v>20</v>
       </c>
       <c r="D22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="15">
         <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H22" s="15">
-        <v>-84.615384615384</v>
+        <v>-90.909090909090</v>
       </c>
       <c r="I22" s="14">
         <v>12</v>
       </c>
       <c r="J22" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K22" s="15">
-        <v>-45.454545454545</v>
+        <v>-47.826086956521</v>
       </c>
       <c r="L22" s="15">
         <v>9.090909090909</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="D24" s="14">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E24" s="15">
-        <v>-61.764705882352</v>
+        <v>12.903225806451</v>
       </c>
       <c r="F24" s="14">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="G24" s="14">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H24" s="15">
-        <v>-30.769230769230</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="I24" s="14">
-        <v>396</v>
+        <v>433</v>
       </c>
       <c r="J24" s="14">
-        <v>401</v>
+        <v>432</v>
       </c>
       <c r="K24" s="15">
-        <v>-1.246882793017</v>
+        <v>0.231481481481</v>
       </c>
       <c r="L24" s="15">
-        <v>-29.787234042553</v>
+        <v>-26.610169491525</v>
       </c>
       <c r="M24" s="15">
-        <v>97.014925373134</v>
+        <v>90.748898678414</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D25" s="14">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E25" s="15">
-        <v>-80</v>
+        <v>6.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G25" s="14">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H25" s="15">
-        <v>-55.223880597014</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I25" s="14">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="J25" s="14">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="K25" s="15">
-        <v>-6.779661016949</v>
+        <v>-5.976095617529</v>
       </c>
       <c r="L25" s="15">
-        <v>-41.489361702127</v>
+        <v>-39.949109414758</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
+        <v>55.555555555555</v>
+      </c>
+      <c r="F26" s="14">
+        <v>44</v>
+      </c>
+      <c r="G26" s="14">
+        <v>44</v>
+      </c>
+      <c r="H26" s="15">
         <v>0</v>
       </c>
-      <c r="F26" s="14">
-        <v>43</v>
-      </c>
-      <c r="G26" s="14">
-        <v>42</v>
-      </c>
-      <c r="H26" s="15">
-        <v>2.380952380952</v>
-      </c>
       <c r="I26" s="14">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="J26" s="14">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="K26" s="15">
-        <v>-9.090909090909</v>
+        <v>-4.964539007092</v>
       </c>
       <c r="L26" s="15">
-        <v>-23.076923076923</v>
+        <v>-18.292682926829</v>
       </c>
       <c r="M26" s="15">
-        <v>-9.774436090225</v>
+        <v>-5.633802816901</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1393,26 +1393,26 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+      <c r="F27" s="14">
+        <v>1</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J27" s="14">
         <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>14.285714285714</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L27" s="15">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
-      </c>
-      <c r="D28" s="14">
-        <v>3</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G28" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I28" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J28" s="14">
         <v>16</v>
       </c>
       <c r="K28" s="15">
-        <v>6.25</v>
+        <v>18.75</v>
       </c>
       <c r="L28" s="15">
-        <v>13.333333333333</v>
+        <v>11.764705882352</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="14">
-        <v>1</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-108pct.xlsx
+++ b/data/source/weekly/cs-en-us-108pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -895,38 +895,38 @@
       <c r="C15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
         <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K15" s="15">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="L15" s="15">
-        <v>133.333333333333</v>
+        <v>166.666666666667</v>
       </c>
       <c r="M15" s="15">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="N15" s="15">
-        <v>250</v>
+        <v>300</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F16" s="14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G16" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H16" s="15">
-        <v>27.777777777777</v>
+        <v>40</v>
       </c>
       <c r="I16" s="14">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J16" s="14">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K16" s="15">
-        <v>12</v>
+        <v>15.686274509803</v>
       </c>
       <c r="L16" s="15">
-        <v>-9.677419354838</v>
+        <v>-15.714285714285</v>
       </c>
       <c r="M16" s="15">
-        <v>3.703703703703</v>
+        <v>7.272727272727</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.769230769230</v>
+        <v>-82.798833819242</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>-66.666666666666</v>
+        <v>60</v>
       </c>
       <c r="F17" s="14">
         <v>21</v>
       </c>
       <c r="G17" s="14">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H17" s="15">
-        <v>-34.375</v>
+        <v>-27.586206896551</v>
       </c>
       <c r="I17" s="14">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="J17" s="14">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K17" s="15">
-        <v>-17.647058823529</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="L17" s="15">
-        <v>16.666666666666</v>
+        <v>13.043478260869</v>
       </c>
       <c r="M17" s="15">
-        <v>100</v>
+        <v>105.263157894737</v>
       </c>
       <c r="N17" s="15">
-        <v>6.060606060606</v>
+        <v>14.705882352941</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
         <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="F18" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G18" s="14">
         <v>14</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I18" s="14">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="J18" s="14">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="K18" s="15">
-        <v>-16.923076923076</v>
+        <v>-14.492753623188</v>
       </c>
       <c r="L18" s="15">
-        <v>-21.739130434782</v>
+        <v>-19.178082191780</v>
       </c>
       <c r="M18" s="15">
-        <v>-30.769230769230</v>
+        <v>-26.25</v>
       </c>
       <c r="N18" s="15">
-        <v>-86.533665835411</v>
+        <v>-86.018957345971</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D19" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E19" s="15">
-        <v>-53.333333333333</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="F19" s="14">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G19" s="14">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H19" s="15">
-        <v>-26.984126984127</v>
+        <v>-22.580645161290</v>
       </c>
       <c r="I19" s="14">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="J19" s="14">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="K19" s="15">
-        <v>5.617977528089</v>
+        <v>4.615384615384</v>
       </c>
       <c r="L19" s="15">
-        <v>-5.050505050505</v>
+        <v>-3.317535545023</v>
       </c>
       <c r="M19" s="15">
-        <v>56.666666666666</v>
+        <v>56.923076923076</v>
       </c>
       <c r="N19" s="15">
-        <v>-7.389162561576</v>
+        <v>-9.734513274336</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D20" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>20</v>
+        <v>700</v>
       </c>
       <c r="F20" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G20" s="14">
         <v>12</v>
       </c>
       <c r="H20" s="15">
-        <v>41.666666666666</v>
+        <v>75</v>
       </c>
       <c r="I20" s="14">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="J20" s="14">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K20" s="15">
-        <v>94.736842105263</v>
+        <v>112.820512820513</v>
       </c>
       <c r="L20" s="15">
-        <v>57.446808510638</v>
+        <v>59.615384615384</v>
       </c>
       <c r="M20" s="15">
-        <v>15.625</v>
+        <v>20.289855072463</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.168224299065</v>
+        <v>-85.489510489510</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D21" s="17">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E21" s="18">
-        <v>-29.729729729729</v>
+        <v>44.827586206896</v>
       </c>
       <c r="F21" s="17">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="G21" s="17">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="H21" s="18">
-        <v>-12.857142857142</v>
+        <v>-3.731343283582</v>
       </c>
       <c r="I21" s="17">
-        <v>449</v>
+        <v>491</v>
       </c>
       <c r="J21" s="17">
-        <v>422</v>
+        <v>451</v>
       </c>
       <c r="K21" s="18">
-        <v>6.398104265402</v>
+        <v>8.869179600886</v>
       </c>
       <c r="L21" s="18">
-        <v>2.277904328018</v>
+        <v>2.719665271966</v>
       </c>
       <c r="M21" s="18">
-        <v>25.418994413407</v>
+        <v>29.551451187335</v>
       </c>
       <c r="N21" s="18">
-        <v>-70.787247885491</v>
+        <v>-70.02442002442</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,20 +1182,20 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="14">
+        <v>7</v>
+      </c>
+      <c r="H22" s="15">
         <v>-100</v>
-      </c>
-      <c r="F22" s="14">
-        <v>1</v>
-      </c>
-      <c r="G22" s="14">
-        <v>11</v>
-      </c>
-      <c r="H22" s="15">
-        <v>-90.909090909090</v>
       </c>
       <c r="I22" s="14">
         <v>12</v>
@@ -1207,10 +1207,10 @@
         <v>-47.826086956521</v>
       </c>
       <c r="L22" s="15">
-        <v>9.090909090909</v>
+        <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>9.090909090909</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1265,34 +1265,34 @@
         <v>35</v>
       </c>
       <c r="D24" s="14">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E24" s="15">
-        <v>12.903225806451</v>
+        <v>52.173913043478</v>
       </c>
       <c r="F24" s="14">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="G24" s="14">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H24" s="15">
-        <v>-15.789473684210</v>
+        <v>-6.034482758620</v>
       </c>
       <c r="I24" s="14">
-        <v>433</v>
+        <v>469</v>
       </c>
       <c r="J24" s="14">
-        <v>432</v>
+        <v>455</v>
       </c>
       <c r="K24" s="15">
-        <v>0.231481481481</v>
+        <v>3.076923076923</v>
       </c>
       <c r="L24" s="15">
-        <v>-26.610169491525</v>
+        <v>-25.791139240506</v>
       </c>
       <c r="M24" s="15">
-        <v>90.748898678414</v>
+        <v>89.112903225806</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D25" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E25" s="15">
-        <v>6.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G25" s="14">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="H25" s="15">
-        <v>-42.857142857142</v>
+        <v>-34.782608695652</v>
       </c>
       <c r="I25" s="14">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="J25" s="14">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="K25" s="15">
-        <v>-5.976095617529</v>
+        <v>-5.576208178438</v>
       </c>
       <c r="L25" s="15">
-        <v>-39.949109414758</v>
+        <v>-40.235294117647</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
         <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>55.555555555555</v>
+        <v>22.222222222222</v>
       </c>
       <c r="F26" s="14">
         <v>44</v>
       </c>
       <c r="G26" s="14">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H26" s="15">
-        <v>0</v>
+        <v>2.325581395348</v>
       </c>
       <c r="I26" s="14">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="J26" s="14">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="K26" s="15">
-        <v>-4.964539007092</v>
+        <v>-3.333333333333</v>
       </c>
       <c r="L26" s="15">
-        <v>-18.292682926829</v>
+        <v>-15.697674418604</v>
       </c>
       <c r="M26" s="15">
-        <v>-5.633802816901</v>
+        <v>-2.027027027027</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K27" s="15">
-        <v>28.571428571428</v>
+        <v>25</v>
       </c>
       <c r="L27" s="15">
-        <v>50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
       </c>
       <c r="F28" s="14">
         <v>9</v>
       </c>
       <c r="G28" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H28" s="15">
-        <v>28.571428571428</v>
+        <v>12.5</v>
       </c>
       <c r="I28" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J28" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K28" s="15">
-        <v>18.75</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>11.764705882352</v>
+        <v>5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1493,8 +1493,8 @@
       <c r="K29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L29" s="13" t="s">
-        <v>21</v>
+      <c r="L29" s="15">
+        <v>-100</v>
       </c>
       <c r="M29" s="15">
         <v>-100</v>
@@ -1534,8 +1534,8 @@
       <c r="K30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L30" s="13" t="s">
-        <v>21</v>
+      <c r="L30" s="15">
+        <v>-100</v>
       </c>
       <c r="M30" s="15">
         <v>-100</v>
@@ -1551,32 +1551,32 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F31" s="14">
+        <v>1</v>
+      </c>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>0</v>
       </c>
       <c r="I31" s="14">
-        <v>2</v>
-      </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="J31" s="14">
+        <v>1</v>
+      </c>
+      <c r="K31" s="15">
+        <v>200</v>
       </c>
       <c r="L31" s="15">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-108pct.xlsx
+++ b/data/source/weekly/cs-en-us-108pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -892,23 +892,23 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>0</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
         <v>8</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>1</v>
+      </c>
+      <c r="D16" s="14">
         <v>4</v>
       </c>
-      <c r="D16" s="14">
-        <v>1</v>
-      </c>
       <c r="E16" s="15">
-        <v>300</v>
+        <v>-75</v>
       </c>
       <c r="F16" s="14">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G16" s="14">
         <v>15</v>
       </c>
       <c r="H16" s="15">
-        <v>40</v>
+        <v>13.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J16" s="14">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K16" s="15">
-        <v>15.686274509803</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L16" s="15">
-        <v>-15.714285714285</v>
+        <v>-20</v>
       </c>
       <c r="M16" s="15">
-        <v>7.272727272727</v>
+        <v>9.090909090909</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.798833819242</v>
+        <v>-83.516483516483</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="F17" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G17" s="14">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H17" s="15">
-        <v>-27.586206896551</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I17" s="14">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="J17" s="14">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="K17" s="15">
-        <v>-13.333333333333</v>
+        <v>-11.702127659574</v>
       </c>
       <c r="L17" s="15">
-        <v>13.043478260869</v>
+        <v>10.666666666666</v>
       </c>
       <c r="M17" s="15">
-        <v>105.263157894737</v>
+        <v>97.619047619047</v>
       </c>
       <c r="N17" s="15">
-        <v>14.705882352941</v>
+        <v>10.666666666666</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="F18" s="14">
         <v>16</v>
       </c>
       <c r="G18" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H18" s="15">
-        <v>14.285714285714</v>
+        <v>23.076923076923</v>
       </c>
       <c r="I18" s="14">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="J18" s="14">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K18" s="15">
-        <v>-14.492753623188</v>
+        <v>-9.859154929577</v>
       </c>
       <c r="L18" s="15">
-        <v>-19.178082191780</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="M18" s="15">
-        <v>-26.25</v>
+        <v>-21.951219512195</v>
       </c>
       <c r="N18" s="15">
-        <v>-86.018957345971</v>
+        <v>-85.650224215246</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D19" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>-5.882352941176</v>
+        <v>15.384615384615</v>
       </c>
       <c r="F19" s="14">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G19" s="14">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="H19" s="15">
-        <v>-22.580645161290</v>
+        <v>-12.280701754386</v>
       </c>
       <c r="I19" s="14">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="J19" s="14">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="K19" s="15">
-        <v>4.615384615384</v>
+        <v>5.288461538461</v>
       </c>
       <c r="L19" s="15">
-        <v>-3.317535545023</v>
+        <v>-1.351351351351</v>
       </c>
       <c r="M19" s="15">
-        <v>56.923076923076</v>
+        <v>54.225352112676</v>
       </c>
       <c r="N19" s="15">
-        <v>-9.734513274336</v>
+        <v>-12.4</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>700</v>
+        <v>57.142857142857</v>
       </c>
       <c r="F20" s="14">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G20" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H20" s="15">
-        <v>75</v>
+        <v>86.666666666666</v>
       </c>
       <c r="I20" s="14">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J20" s="14">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="K20" s="15">
-        <v>112.820512820513</v>
+        <v>104.347826086957</v>
       </c>
       <c r="L20" s="15">
-        <v>59.615384615384</v>
+        <v>67.857142857142</v>
       </c>
       <c r="M20" s="15">
-        <v>20.289855072463</v>
+        <v>27.027027027027</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.489510489510</v>
+        <v>-84.514003294892</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,72 +1139,72 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D21" s="17">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E21" s="18">
-        <v>44.827586206896</v>
+        <v>23.333333333333</v>
       </c>
       <c r="F21" s="17">
+        <v>137</v>
+      </c>
+      <c r="G21" s="17">
         <v>129</v>
       </c>
-      <c r="G21" s="17">
-        <v>134</v>
-      </c>
       <c r="H21" s="18">
-        <v>-3.731343283582</v>
+        <v>6.201550387596</v>
       </c>
       <c r="I21" s="17">
-        <v>491</v>
+        <v>528</v>
       </c>
       <c r="J21" s="17">
-        <v>451</v>
+        <v>481</v>
       </c>
       <c r="K21" s="18">
-        <v>8.869179600886</v>
+        <v>9.771309771309</v>
       </c>
       <c r="L21" s="18">
-        <v>2.719665271966</v>
+        <v>4.142011834319</v>
       </c>
       <c r="M21" s="18">
-        <v>29.551451187335</v>
+        <v>31.343283582089</v>
       </c>
       <c r="N21" s="18">
-        <v>-70.02442002442</v>
+        <v>-69.811320754717</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
+      </c>
+      <c r="D22" s="14">
+        <v>3</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="F22" s="14">
+        <v>1</v>
       </c>
       <c r="G22" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H22" s="15">
-        <v>-100</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="I22" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J22" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K22" s="15">
-        <v>-47.826086956521</v>
+        <v>-50</v>
       </c>
       <c r="L22" s="15">
         <v>0</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D24" s="14">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="E24" s="15">
-        <v>52.173913043478</v>
+        <v>-20.512820512820</v>
       </c>
       <c r="F24" s="14">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="G24" s="14">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="H24" s="15">
-        <v>-6.034482758620</v>
+        <v>-7.874015748031</v>
       </c>
       <c r="I24" s="14">
-        <v>469</v>
+        <v>500</v>
       </c>
       <c r="J24" s="14">
-        <v>455</v>
+        <v>494</v>
       </c>
       <c r="K24" s="15">
-        <v>3.076923076923</v>
+        <v>1.214574898785</v>
       </c>
       <c r="L24" s="15">
-        <v>-25.791139240506</v>
+        <v>-25.261584454409</v>
       </c>
       <c r="M24" s="15">
-        <v>89.112903225806</v>
+        <v>76.056338028169</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D25" s="14">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="F25" s="14">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G25" s="14">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H25" s="15">
-        <v>-34.782608695652</v>
+        <v>-27.631578947368</v>
       </c>
       <c r="I25" s="14">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="J25" s="14">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="K25" s="15">
-        <v>-5.576208178438</v>
+        <v>-7.191780821917</v>
       </c>
       <c r="L25" s="15">
-        <v>-40.235294117647</v>
+        <v>-39.911308203991</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E26" s="15">
-        <v>22.222222222222</v>
+        <v>7.142857142857</v>
       </c>
       <c r="F26" s="14">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G26" s="14">
         <v>43</v>
       </c>
       <c r="H26" s="15">
-        <v>2.325581395348</v>
+        <v>18.604651162790</v>
       </c>
       <c r="I26" s="14">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="J26" s="14">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="K26" s="15">
-        <v>-3.333333333333</v>
+        <v>-2.439024390243</v>
       </c>
       <c r="L26" s="15">
-        <v>-15.697674418604</v>
+        <v>-12.568306010929</v>
       </c>
       <c r="M26" s="15">
-        <v>-2.027027027027</v>
+        <v>2.564102564102</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,23 +1384,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>0</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
         <v>10</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>2</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
         <v>2</v>
       </c>
       <c r="E28" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F28" s="14">
+        <v>7</v>
+      </c>
+      <c r="G28" s="14">
+        <v>7</v>
+      </c>
+      <c r="H28" s="15">
         <v>0</v>
       </c>
-      <c r="F28" s="14">
-        <v>9</v>
-      </c>
-      <c r="G28" s="14">
-        <v>8</v>
-      </c>
-      <c r="H28" s="15">
-        <v>12.5</v>
-      </c>
       <c r="I28" s="14">
         <v>21</v>
       </c>
       <c r="J28" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K28" s="15">
-        <v>16.666666666666</v>
+        <v>5</v>
       </c>
       <c r="L28" s="15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1561,19 +1561,19 @@
         <v>1</v>
       </c>
       <c r="G31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I31" s="14">
         <v>3</v>
       </c>
       <c r="J31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="L31" s="15">
         <v>-40</v>
@@ -1617,7 +1617,7 @@
         <v>21</v>
       </c>
       <c r="F33" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1635,7 +1635,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-108pct.xlsx
+++ b/data/source/weekly/cs-en-us-108pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
       </c>
       <c r="F15" s="14">
+        <v>4</v>
+      </c>
+      <c r="G15" s="14">
         <v>2</v>
-      </c>
-      <c r="G15" s="14">
-        <v>1</v>
       </c>
       <c r="H15" s="15">
         <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K15" s="15">
-        <v>60</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L15" s="15">
-        <v>166.666666666667</v>
+        <v>150</v>
       </c>
       <c r="M15" s="15">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="N15" s="15">
-        <v>300</v>
+        <v>400</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>-75</v>
+        <v>50</v>
       </c>
       <c r="F16" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G16" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H16" s="15">
-        <v>13.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I16" s="14">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J16" s="14">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K16" s="15">
-        <v>9.090909090909</v>
+        <v>10.526315789473</v>
       </c>
       <c r="L16" s="15">
-        <v>-20</v>
+        <v>-25.882352941176</v>
       </c>
       <c r="M16" s="15">
-        <v>9.090909090909</v>
+        <v>10.526315789473</v>
       </c>
       <c r="N16" s="15">
-        <v>-83.516483516483</v>
+        <v>-83.678756476683</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
         <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G17" s="14">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="H17" s="15">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="J17" s="14">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="K17" s="15">
-        <v>-11.702127659574</v>
+        <v>-11.224489795918</v>
       </c>
       <c r="L17" s="15">
-        <v>10.666666666666</v>
+        <v>8.75</v>
       </c>
       <c r="M17" s="15">
-        <v>97.619047619047</v>
+        <v>89.130434782608</v>
       </c>
       <c r="N17" s="15">
-        <v>10.666666666666</v>
+        <v>6.097560975609</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
         <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>150</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G18" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H18" s="15">
-        <v>23.076923076923</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J18" s="14">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K18" s="15">
-        <v>-9.859154929577</v>
+        <v>-10.958904109589</v>
       </c>
       <c r="L18" s="15">
-        <v>-15.789473684210</v>
+        <v>-17.721518987341</v>
       </c>
       <c r="M18" s="15">
-        <v>-21.951219512195</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="N18" s="15">
-        <v>-85.650224215246</v>
+        <v>-86.051502145922</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E19" s="15">
-        <v>15.384615384615</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F19" s="14">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G19" s="14">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="H19" s="15">
-        <v>-12.280701754386</v>
+        <v>-17.460317460317</v>
       </c>
       <c r="I19" s="14">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="J19" s="14">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="K19" s="15">
-        <v>5.288461538461</v>
+        <v>3.097345132743</v>
       </c>
       <c r="L19" s="15">
-        <v>-1.351351351351</v>
+        <v>-2.100840336134</v>
       </c>
       <c r="M19" s="15">
-        <v>54.225352112676</v>
+        <v>56.375838926174</v>
       </c>
       <c r="N19" s="15">
-        <v>-12.4</v>
+        <v>-12.734082397003</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D20" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>57.142857142857</v>
+        <v>233.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G20" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H20" s="15">
-        <v>86.666666666666</v>
+        <v>125</v>
       </c>
       <c r="I20" s="14">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J20" s="14">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K20" s="15">
-        <v>104.347826086957</v>
+        <v>112.244897959184</v>
       </c>
       <c r="L20" s="15">
-        <v>67.857142857142</v>
+        <v>76.271186440678</v>
       </c>
       <c r="M20" s="15">
-        <v>27.027027027027</v>
+        <v>30</v>
       </c>
       <c r="N20" s="15">
-        <v>-84.514003294892</v>
+        <v>-83.775351014040</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D21" s="17">
         <v>30</v>
       </c>
       <c r="E21" s="18">
-        <v>23.333333333333</v>
+        <v>10</v>
       </c>
       <c r="F21" s="17">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G21" s="17">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H21" s="18">
-        <v>6.201550387596</v>
+        <v>10.317460317460</v>
       </c>
       <c r="I21" s="17">
-        <v>528</v>
+        <v>562</v>
       </c>
       <c r="J21" s="17">
-        <v>481</v>
+        <v>511</v>
       </c>
       <c r="K21" s="18">
-        <v>9.771309771309</v>
+        <v>9.980430528375</v>
       </c>
       <c r="L21" s="18">
-        <v>4.142011834319</v>
+        <v>3.119266055045</v>
       </c>
       <c r="M21" s="18">
-        <v>31.343283582089</v>
+        <v>32.547169811320</v>
       </c>
       <c r="N21" s="18">
-        <v>-69.811320754717</v>
+        <v>-69.605191995673</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,28 +1183,28 @@
         <v>1</v>
       </c>
       <c r="D22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E22" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="F22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H22" s="15">
-        <v>-83.333333333333</v>
+        <v>-75</v>
       </c>
       <c r="I22" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J22" s="14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K22" s="15">
-        <v>-50</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="L22" s="15">
         <v>0</v>
@@ -1265,34 +1265,34 @@
         <v>31</v>
       </c>
       <c r="D24" s="14">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="E24" s="15">
-        <v>-20.512820512820</v>
+        <v>19.230769230769</v>
       </c>
       <c r="F24" s="14">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="G24" s="14">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="H24" s="15">
-        <v>-7.874015748031</v>
+        <v>10.924369747899</v>
       </c>
       <c r="I24" s="14">
-        <v>500</v>
+        <v>531</v>
       </c>
       <c r="J24" s="14">
-        <v>494</v>
+        <v>520</v>
       </c>
       <c r="K24" s="15">
-        <v>1.214574898785</v>
+        <v>2.115384615384</v>
       </c>
       <c r="L24" s="15">
-        <v>-25.261584454409</v>
+        <v>-24.251069900142</v>
       </c>
       <c r="M24" s="15">
-        <v>76.056338028169</v>
+        <v>77.591973244147</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D25" s="14">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E25" s="15">
-        <v>-26.086956521739</v>
+        <v>7.692307692307</v>
       </c>
       <c r="F25" s="14">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="G25" s="14">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="H25" s="15">
-        <v>-27.631578947368</v>
+        <v>-5.797101449275</v>
       </c>
       <c r="I25" s="14">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="J25" s="14">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="K25" s="15">
-        <v>-7.191780821917</v>
+        <v>-6.557377049180</v>
       </c>
       <c r="L25" s="15">
-        <v>-39.911308203991</v>
+        <v>-39.490445859872</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D26" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>7.142857142857</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G26" s="14">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H26" s="15">
-        <v>18.604651162790</v>
+        <v>27.272727272727</v>
       </c>
       <c r="I26" s="14">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="J26" s="14">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="K26" s="15">
-        <v>-2.439024390243</v>
+        <v>0</v>
       </c>
       <c r="L26" s="15">
-        <v>-12.568306010929</v>
+        <v>-14.975845410628</v>
       </c>
       <c r="M26" s="15">
-        <v>2.564102564102</v>
+        <v>6.666666666666</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="14">
+        <v>2</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>100</v>
       </c>
       <c r="F27" s="14">
+        <v>5</v>
+      </c>
+      <c r="G27" s="14">
         <v>2</v>
       </c>
-      <c r="G27" s="14">
-        <v>1</v>
-      </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="I27" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J27" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>25</v>
+        <v>44.444444444444</v>
       </c>
       <c r="L27" s="15">
-        <v>66.666666666666</v>
+        <v>85.714285714285</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>3</v>
       </c>
       <c r="D28" s="14">
         <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>50</v>
       </c>
       <c r="F28" s="14">
         <v>7</v>
       </c>
       <c r="G28" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J28" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K28" s="15">
-        <v>5</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,29 +1469,29 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>-100</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K29" s="13" t="s">
-        <v>21</v>
+      <c r="J29" s="14">
+        <v>1</v>
+      </c>
+      <c r="K29" s="15">
+        <v>-100</v>
       </c>
       <c r="L29" s="15">
         <v>-100</v>
@@ -1510,29 +1510,29 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>-100</v>
       </c>
       <c r="I30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K30" s="13" t="s">
-        <v>21</v>
+      <c r="J30" s="14">
+        <v>1</v>
+      </c>
+      <c r="K30" s="15">
+        <v>-100</v>
       </c>
       <c r="L30" s="15">
         <v>-100</v>
@@ -1551,20 +1551,20 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F31" s="14">
-        <v>1</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="14">
         <v>2</v>
       </c>
       <c r="H31" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I31" s="14">
         <v>3</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="14">
-        <v>1</v>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-108pct.xlsx
+++ b/data/source/weekly/cs-en-us-108pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -878,8 +878,8 @@
       <c r="K14" s="15">
         <v>-100</v>
       </c>
-      <c r="L14" s="13" t="s">
-        <v>21</v>
+      <c r="L14" s="15">
+        <v>-100</v>
       </c>
       <c r="M14" s="15">
         <v>-100</v>
@@ -892,38 +892,38 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="14">
         <v>1</v>
       </c>
       <c r="E15" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F15" s="14">
+        <v>3</v>
+      </c>
+      <c r="G15" s="14">
+        <v>3</v>
+      </c>
+      <c r="H15" s="15">
         <v>0</v>
-      </c>
-      <c r="F15" s="14">
-        <v>4</v>
-      </c>
-      <c r="G15" s="14">
-        <v>2</v>
-      </c>
-      <c r="H15" s="15">
-        <v>100</v>
       </c>
       <c r="I15" s="14">
         <v>10</v>
       </c>
       <c r="J15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>66.666666666666</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L15" s="15">
         <v>150</v>
       </c>
       <c r="M15" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N15" s="15">
         <v>400</v>
@@ -943,31 +943,31 @@
         <v>50</v>
       </c>
       <c r="F16" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G16" s="14">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>22.222222222222</v>
       </c>
       <c r="I16" s="14">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J16" s="14">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K16" s="15">
-        <v>10.526315789473</v>
+        <v>11.864406779661</v>
       </c>
       <c r="L16" s="15">
-        <v>-25.882352941176</v>
+        <v>-27.472527472527</v>
       </c>
       <c r="M16" s="15">
-        <v>10.526315789473</v>
+        <v>10</v>
       </c>
       <c r="N16" s="15">
-        <v>-83.678756476683</v>
+        <v>-83.941605839416</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F17" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G17" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I17" s="14">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="J17" s="14">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="K17" s="15">
-        <v>-11.224489795918</v>
+        <v>-12.380952380952</v>
       </c>
       <c r="L17" s="15">
-        <v>8.75</v>
+        <v>8.235294117647</v>
       </c>
       <c r="M17" s="15">
-        <v>89.130434782608</v>
+        <v>84</v>
       </c>
       <c r="N17" s="15">
-        <v>6.097560975609</v>
+        <v>3.370786516853</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F18" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G18" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H18" s="15">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="J18" s="14">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="K18" s="15">
-        <v>-10.958904109589</v>
+        <v>-13.75</v>
       </c>
       <c r="L18" s="15">
-        <v>-17.721518987341</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="M18" s="15">
-        <v>-23.529411764705</v>
+        <v>-24.175824175824</v>
       </c>
       <c r="N18" s="15">
-        <v>-86.051502145922</v>
+        <v>-85.947046843177</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D19" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E19" s="15">
-        <v>-22.222222222222</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="F19" s="14">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G19" s="14">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H19" s="15">
-        <v>-17.460317460317</v>
+        <v>-12.307692307692</v>
       </c>
       <c r="I19" s="14">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="J19" s="14">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="K19" s="15">
-        <v>3.097345132743</v>
+        <v>0.823045267489</v>
       </c>
       <c r="L19" s="15">
-        <v>-2.100840336134</v>
+        <v>-4.296875</v>
       </c>
       <c r="M19" s="15">
-        <v>56.375838926174</v>
+        <v>56.050955414012</v>
       </c>
       <c r="N19" s="15">
-        <v>-12.734082397003</v>
+        <v>-15.224913494809</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D20" s="14">
         <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>233.333333333333</v>
+        <v>133.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G20" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H20" s="15">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="I20" s="14">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="J20" s="14">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K20" s="15">
-        <v>112.244897959184</v>
+        <v>111.538461538462</v>
       </c>
       <c r="L20" s="15">
-        <v>76.271186440678</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M20" s="15">
-        <v>30</v>
+        <v>32.530120481927</v>
       </c>
       <c r="N20" s="15">
-        <v>-83.775351014040</v>
+        <v>-83.870967741935</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D21" s="17">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E21" s="18">
-        <v>10</v>
+        <v>-8.108108108108</v>
       </c>
       <c r="F21" s="17">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G21" s="17">
         <v>126</v>
       </c>
       <c r="H21" s="18">
-        <v>10.317460317460</v>
+        <v>13.492063492063</v>
       </c>
       <c r="I21" s="17">
-        <v>562</v>
+        <v>592</v>
       </c>
       <c r="J21" s="17">
-        <v>511</v>
+        <v>548</v>
       </c>
       <c r="K21" s="18">
-        <v>9.980430528375</v>
+        <v>8.029197080291</v>
       </c>
       <c r="L21" s="18">
-        <v>3.119266055045</v>
+        <v>1.369863013698</v>
       </c>
       <c r="M21" s="18">
-        <v>32.547169811320</v>
+        <v>31.848552338530</v>
       </c>
       <c r="N21" s="18">
-        <v>-69.605191995673</v>
+        <v>-69.933976637887</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,34 +1180,34 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="14">
+        <v>2</v>
+      </c>
+      <c r="E22" s="15">
+        <v>0</v>
+      </c>
+      <c r="F22" s="14">
         <v>4</v>
       </c>
-      <c r="E22" s="15">
-        <v>-75</v>
-      </c>
-      <c r="F22" s="14">
-        <v>2</v>
-      </c>
       <c r="G22" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H22" s="15">
-        <v>-75</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="I22" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J22" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K22" s="15">
-        <v>-53.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>6.666666666666</v>
       </c>
       <c r="M22" s="15">
         <v>0</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D24" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E24" s="15">
-        <v>19.230769230769</v>
+        <v>-17.241379310344</v>
       </c>
       <c r="F24" s="14">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="G24" s="14">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H24" s="15">
-        <v>10.924369747899</v>
+        <v>4.273504273504</v>
       </c>
       <c r="I24" s="14">
-        <v>531</v>
+        <v>556</v>
       </c>
       <c r="J24" s="14">
-        <v>520</v>
+        <v>549</v>
       </c>
       <c r="K24" s="15">
-        <v>2.115384615384</v>
+        <v>1.275045537340</v>
       </c>
       <c r="L24" s="15">
-        <v>-24.251069900142</v>
+        <v>-24.250681198910</v>
       </c>
       <c r="M24" s="15">
-        <v>77.591973244147</v>
+        <v>75.949367088607</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D25" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E25" s="15">
-        <v>7.692307692307</v>
+        <v>-43.75</v>
       </c>
       <c r="F25" s="14">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G25" s="14">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H25" s="15">
-        <v>-5.797101449275</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I25" s="14">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="J25" s="14">
-        <v>305</v>
+        <v>321</v>
       </c>
       <c r="K25" s="15">
-        <v>-6.557377049180</v>
+        <v>-8.099688473520</v>
       </c>
       <c r="L25" s="15">
-        <v>-39.490445859872</v>
+        <v>-40.040650406504</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G26" s="14">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H26" s="15">
-        <v>27.272727272727</v>
+        <v>20.930232558139</v>
       </c>
       <c r="I26" s="14">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="J26" s="14">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="K26" s="15">
-        <v>0</v>
+        <v>1.086956521739</v>
       </c>
       <c r="L26" s="15">
-        <v>-14.975845410628</v>
+        <v>-16.591928251121</v>
       </c>
       <c r="M26" s="15">
-        <v>6.666666666666</v>
+        <v>5.084745762711</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>2</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J27" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K27" s="15">
-        <v>44.444444444444</v>
+        <v>20</v>
       </c>
       <c r="L27" s="15">
-        <v>85.714285714285</v>
+        <v>50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1435,25 +1435,25 @@
         <v>50</v>
       </c>
       <c r="F28" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H28" s="15">
+        <v>12.5</v>
+      </c>
+      <c r="I28" s="14">
+        <v>28</v>
+      </c>
+      <c r="J28" s="14">
+        <v>24</v>
+      </c>
+      <c r="K28" s="15">
         <v>16.666666666666</v>
       </c>
-      <c r="I28" s="14">
-        <v>24</v>
-      </c>
-      <c r="J28" s="14">
-        <v>22</v>
-      </c>
-      <c r="K28" s="15">
-        <v>9.090909090909</v>
-      </c>
       <c r="L28" s="15">
-        <v>14.285714285714</v>
+        <v>21.739130434782</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1557,14 +1557,14 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="14">
         <v>2</v>
       </c>
       <c r="H31" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="I31" s="14">
         <v>3</v>
